--- a/data/bryan/output/bryan_gto.xlsx
+++ b/data/bryan/output/bryan_gto.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bryan Backsway HC qcb2,4 (+8)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bryan Backsway (+8)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bryan 4,1 (+7) or 4,1b (+8) SNE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bryan Backsway HC qcb2,4 (+8)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bryan Backsway (+8)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,9 +36,6 @@
       <sz val="18"/>
     </font>
     <font>
-      <color rgb="007F6000"/>
-    </font>
-    <font>
       <b val="1"/>
       <color rgb="00333333"/>
       <sz val="12"/>
@@ -51,8 +49,20 @@
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <color rgb="00006100"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="FF9C0006"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="007F6000"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -61,14 +71,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="004F81BD"/>
+        <bgColor rgb="004F81BD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004F81BD"/>
-        <bgColor rgb="004F81BD"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -93,31 +115,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -488,16 +516,16 @@
   <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="68" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bryan Backsway HC qcb2,4 (+8)</t>
+          <t>Bryan 4,1 (+7) or 4,1b (+8) SNE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -522,7 +550,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Reina</t>
         </is>
@@ -534,8 +562,8 @@
           <t>Payoff</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
-        <v>9.800000000000001</v>
+      <c r="B4" s="6" t="n">
+        <v>10.2</v>
       </c>
     </row>
     <row r="5">
@@ -544,141 +572,141 @@
           <t>Comment</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Bryan Backsway (+8) after 4,1b i12 punish with qcb 2,4 hit confirm</t>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Bryan 4,1 (+7) and 4,1b (+8) after i12 punish with no hit confirm (w/snake eyes)</t>
         </is>
       </c>
     </row>
     <row r="6"/>
     <row r="7"/>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>distribution</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>strategy_value</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Bryan</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>qcb1</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>0.04373956594323873</v>
-      </c>
-      <c r="D9" s="8" t="n">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>SWA.1</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>0.03850891757270634</v>
+      </c>
+      <c r="D9" s="4" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Bryan</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>qcb2,4</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>0.5395659432387312</v>
-      </c>
-      <c r="D10" s="8" t="n">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>SWA.3</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>0.3556317283487762</v>
+      </c>
+      <c r="D10" s="4" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Bryan</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>qcb3</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>0.4166944908180301</v>
-      </c>
-      <c r="D11" s="8" t="n">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>incinerator</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>0.6058593540785175</v>
+      </c>
+      <c r="D11" s="4" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Reina</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n">
-        <v>0.839017409968996</v>
-      </c>
-      <c r="D12" s="8" t="n">
+      <c r="C12" s="11" t="n">
+        <v>0.844518236837877</v>
+      </c>
+      <c r="D12" s="5" t="n">
         <v>-10</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Reina</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Hop Kick</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
-        <v>0.1161459575482948</v>
-      </c>
-      <c r="D13" s="8" t="n">
+      <c r="C13" s="11" t="n">
+        <v>0.115740988699052</v>
+      </c>
+      <c r="D13" s="5" t="n">
         <v>-10</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Reina</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Low parry</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n">
-        <v>0.04483663248270928</v>
-      </c>
-      <c r="D14" s="8" t="n">
+      <c r="C14" s="11" t="n">
+        <v>0.03974077446307107</v>
+      </c>
+      <c r="D14" s="5" t="n">
         <v>-10</v>
       </c>
     </row>
@@ -699,8 +727,219 @@
   <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bryan Backsway HC qcb2,4 (+8)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Reina</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Payoff</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Bryan Backsway (+8) after 4,1b i12 punish with qcb 2,4 hit confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>distribution</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>strategy_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>qcb1</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>0.04373956594323873</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>qcb2,4</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>0.5395659432387312</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>qcb3</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>0.4166944908180301</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Reina</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>0.839017409968996</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Reina</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Hop Kick</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>0.1161459575482948</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Reina</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Low parry</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>0.04483663248270928</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="63" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
@@ -733,7 +972,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Reina</t>
         </is>
@@ -745,7 +984,7 @@
           <t>Payoff</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="6" t="n">
         <v>4.3</v>
       </c>
     </row>
@@ -755,7 +994,7 @@
           <t>Comment</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Bryan Backsway (+8) after 4,1b i12 punish with no hit confirm</t>
         </is>
@@ -764,132 +1003,132 @@
     <row r="6"/>
     <row r="7"/>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>distribution</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>strategy_value</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Bryan</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>qcb2</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="10" t="n">
         <v>0.797198538367844</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="4" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Bryan</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>qcb3</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="10" t="n">
         <v>0.1875761266747868</v>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D10" s="4" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Bryan</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="10" t="n">
         <v>0.01522533495736906</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="4" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Reina</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="11" t="n">
         <v>0.7408647990255786</v>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D12" s="5" t="n">
         <v>-4</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Reina</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Hop Kick</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="11" t="n">
         <v>0.05602923264311815</v>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="5" t="n">
         <v>-4</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Reina</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Low parry</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="11" t="n">
         <v>0.2031059683313033</v>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D14" s="5" t="n">
         <v>-4</v>
       </c>
     </row>

--- a/data/bryan/output/bryan_gto.xlsx
+++ b/data/bryan/output/bryan_gto.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bryan 4,1 (+7) or 4,1b (+8) SNE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bryan Backsway HC qcb2,4 (+8)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bryan Backsway (+8)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bryan 4,1 (+7) or 4,1b (+8)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bryan 4,1 (+7) or 4,1b (+8) SNE" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bryan QCB1 (+5)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bryan QCB1 (+5) with SNE" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,11 +514,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
@@ -525,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bryan 4,1 (+7) or 4,1b (+8) SNE</t>
+          <t>Bryan 4,1 (+7) or 4,1b (+8)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -563,7 +564,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>10.2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="5">
@@ -574,7 +575,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Bryan 4,1 (+7) and 4,1b (+8) after i12 punish with no hit confirm (w/snake eyes)</t>
+          <t>Bryan 4,1 (+7) and 4,1b (+8) after i12 punish with no hit confirm (w/ no snake eyes)</t>
         </is>
       </c>
     </row>
@@ -610,14 +611,14 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SWA.1</t>
+          <t>SWA.2</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>0.03850891757270634</v>
+        <v>0.6704942586120819</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -632,10 +633,10 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>0.3556317283487762</v>
+        <v>0.1937094358462307</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -646,14 +647,14 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>incinerator</t>
+          <t>f3</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>0.6058593540785175</v>
+        <v>0.1357963055416875</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -668,10 +669,10 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>0.844518236837877</v>
+        <v>0.6221335556986236</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="13">
@@ -682,14 +683,14 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Hop Kick</t>
+          <t>SSL~b</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0.115740988699052</v>
+        <v>0.01476290925541982</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="14">
@@ -700,14 +701,50 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
+          <t>SSL</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>0.005741387918122816</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Reina</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>SSR~b</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>0.08464622101699996</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Reina</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
           <t>Low parry</t>
         </is>
       </c>
-      <c r="C14" s="11" t="n">
-        <v>0.03974077446307107</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>-10</v>
+      <c r="C16" s="11" t="n">
+        <v>0.2727159261108337</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-4</v>
       </c>
     </row>
   </sheetData>
@@ -727,16 +764,16 @@
   <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bryan Backsway HC qcb2,4 (+8)</t>
+          <t>Bryan 4,1 (+7) or 4,1b (+8) SNE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -774,7 +811,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>9.800000000000001</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="5">
@@ -785,7 +822,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Bryan Backsway (+8) after 4,1b i12 punish with qcb 2,4 hit confirm</t>
+          <t>Bryan 4,1 (+7) and 4,1b (+8) after i12 punish with no hit confirm (w/snake eyes)</t>
         </is>
       </c>
     </row>
@@ -821,11 +858,11 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>qcb1</t>
+          <t>SWA.1</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>0.04373956594323873</v>
+        <v>0.03850891757270634</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>10</v>
@@ -839,11 +876,11 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>qcb2,4</t>
+          <t>SWA.3</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>0.5395659432387312</v>
+        <v>0.3556317283487762</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>10</v>
@@ -857,11 +894,11 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>qcb3</t>
+          <t>incinerator</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>0.4166944908180301</v>
+        <v>0.6058593540785175</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>10</v>
@@ -879,7 +916,7 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>0.839017409968996</v>
+        <v>0.844518236837877</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>-10</v>
@@ -897,7 +934,7 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0.1161459575482948</v>
+        <v>0.115740988699052</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>-10</v>
@@ -915,7 +952,7 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>0.04483663248270928</v>
+        <v>0.03974077446307107</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>-10</v>
@@ -935,11 +972,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
@@ -947,7 +984,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bryan Backsway (+8)</t>
+          <t>Bryan QCB1 (+5)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -985,7 +1022,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="5">
@@ -996,7 +1033,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Bryan Backsway (+8) after 4,1b i12 punish with no hit confirm</t>
+          <t>Bryan QCB1 (w/ no snake eyes)</t>
         </is>
       </c>
     </row>
@@ -1032,14 +1069,14 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>qcb2</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>0.797198538367844</v>
+        <v>0.1318105345004203</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1054,10 +1091,10 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>0.1875761266747868</v>
+        <v>0.248225775472238</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1068,32 +1105,351 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>d2</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>0.188204325193125</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>1+2</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>0.06303740585709845</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>df2,1</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>0.3591351645130252</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>db2</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>0.009586794464093062</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Reina</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>SSL~b</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>0.05710957281808771</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Reina</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>SSL</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>0.08862387591810426</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Reina</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>0.3806326793034251</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Reina</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Power Crush</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>0.04532039439072268</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Reina</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Low parry</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>0.2869166122340346</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Reina</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>backdash</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>0.1413968653356256</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bryan QCB1 (+5) with SNE</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Reina</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Payoff</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Bryan QCB1 (w/snake eyes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>distribution</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>strategy_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
+      <c r="C9" s="10" t="n">
+        <v>0.0996369020724345</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>qcb3</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>0.026889388503895</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>incinerator</t>
+        </is>
+      </c>
       <c r="C11" s="10" t="n">
-        <v>0.01522533495736906</v>
+        <v>0.6796708710539638</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Reina</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="n">
-        <v>0.7408647990255786</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>-4</v>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Bryan</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>d4</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>0.1938028383697066</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1104,14 +1460,14 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Hop Kick</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0.05602923264311815</v>
+        <v>0.2620727532810225</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="14">
@@ -1122,14 +1478,104 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Low parry</t>
+          <t>112</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>0.2031059683313033</v>
+        <v>0.1929263950962727</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>-4</v>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Reina</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>DB1</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>0.03220520748841843</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Reina</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>SSL~b</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>0.0738597878056583</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Reina</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>SSL</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>0.08466021658326016</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Reina</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>0.2643721573803865</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Reina</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Hop Kick</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>0.08990348236498147</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-5</v>
       </c>
     </row>
   </sheetData>
